--- a/results/Int Task Remove ACC -0.4/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000993523772169005</v>
+        <v>-0.0003985246601812185</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.002156734630915875</v>
+        <v>0.003176544675375016</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0002786788601422194</v>
+        <v>0.001905744315552773</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0004718607711513644</v>
+        <v>-0.001598568933965603</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0001611676502898274</v>
+        <v>0.002686409070720563</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000654585081491268</v>
+        <v>0.001699366809666684</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0001130553051743744</v>
+        <v>0.0003265320209978817</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001834496144031608</v>
+        <v>-0.001010938631087429</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004782916733902536</v>
+        <v>0.008318990121758999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009255538729656215</v>
+        <v>0.01374298260174444</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.002412877238333144</v>
+        <v>-9.980819653140564e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008025811601532129</v>
+        <v>0.001540938658453708</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002814908188839699</v>
+        <v>0.003823299431884144</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002234110703813558</v>
+        <v>0.00709603350564781</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006548681256341125</v>
+        <v>0.00669912786315126</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.003233350744803045</v>
+        <v>0.0006682525016901852</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00240366548795987</v>
+        <v>-0.0003850336239443586</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0009072503764317771</v>
+        <v>-0.002136171634502807</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00200340665031586</v>
+        <v>0.0007806842360416687</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000139503032126117</v>
+        <v>0.0001590040683052984</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0002690185450088045</v>
+        <v>-0.0001569373452780011</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.000650336763624173</v>
+        <v>-0.0008038813070288385</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001488040854906488</v>
+        <v>0.002091565975381442</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001180990160207998</v>
+        <v>0.0005311779993717679</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.001019440760641749</v>
+        <v>0.000385704695404997</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0002469666766313727</v>
+        <v>0.0001179186122453024</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0040406265272061</v>
+        <v>0.004756960784849486</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.002161525455807741</v>
+        <v>-0.002249824752671422</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.002428397257331127</v>
+        <v>-0.001854737368979752</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.468968571979986e-05</v>
+        <v>-0.001074303669331862</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0008912947781611957</v>
+        <v>-8.215072120492099e-06</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0003287872944053505</v>
+        <v>2.463759543092749e-05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.001102460678270752</v>
+        <v>-0.001475240492391257</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.001399018891994993</v>
+        <v>-0.00159879230396628</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.000742082987952133</v>
+        <v>-0.0004337350153460474</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.001100068493118034</v>
+        <v>-0.0002278979043922069</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0001799085350568188</v>
+        <v>0.001649345594714111</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.001133244381476006</v>
+        <v>-0.002090090453359593</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0008226567057406165</v>
+        <v>0.0003813042821991696</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.000319938711993627</v>
+        <v>0.0003650250021966529</v>
       </c>
       <c r="AR3" t="n">
-        <v>-9.575469825172213e-05</v>
+        <v>-0.00175056037511654</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0002003936957225982</v>
+        <v>0.00201158859179897</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.004472559776603739</v>
+        <v>-0.003929277669714269</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.001995443169676801</v>
+        <v>0.002915988283661871</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.001066869246849549</v>
+        <v>0.0006848127829431882</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.001701135949478358</v>
+        <v>0.0002080960682252996</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.406472563515999e-06</v>
+        <v>-6.87840434278364e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.100546584758773e-05</v>
+        <v>-0.0004820279741998378</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.001573614677129647</v>
+        <v>-0.002266677099340768</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.004568732497728887</v>
+        <v>-0.00438757721505541</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.0069752349060736</v>
+        <v>-0.002778091511713247</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0002505497235508125</v>
+        <v>-0.0001078309837295733</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.833546058773952e-05</v>
+        <v>-0.0001246842349229294</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.001238780534329316</v>
+        <v>-0.0002289162022870817</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.005436371952079994</v>
+        <v>-0.002325515328758152</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.001599983617521369</v>
+        <v>-0.004167014515119374</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.000139095125441312</v>
+        <v>-0.0001545501652809778</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.574938499369301e-05</v>
+        <v>-0.000787110023472143</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.006278919730576015</v>
+        <v>-0.003343913206287187</v>
       </c>
       <c r="BL3" t="n">
-        <v>5.336648009785505e-05</v>
+        <v>-0.0001913197813493406</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.001682930898722389</v>
+        <v>0.00044352931263683</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.00770186581642014</v>
+        <v>-0.00341740473943961</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.001587338277381073</v>
+        <v>0.003866648481917698</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.002354988831897691</v>
+        <v>0.001991667155861486</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.571191779381822e-06</v>
+        <v>0.0001345989692662586</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.001921809249045103</v>
+        <v>0.001801605715165709</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.001099706556209896</v>
+        <v>-8.356114939961679e-05</v>
       </c>
       <c r="BT3" t="n">
-        <v>-8.601719217681717e-05</v>
+        <v>-7.229588217712907e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.007330559384448682</v>
+        <v>0.007671321886731896</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0005609744849469</v>
+        <v>0.001722217301988791</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.00267864677827434</v>
+        <v>0.00134038493223876</v>
       </c>
       <c r="BX3" t="n">
-        <v>-3.273510000939567e-06</v>
+        <v>3.521458200312688e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0003982984889918506</v>
+        <v>7.687573131787469e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-2.967367744366788e-05</v>
+        <v>0.0004972575944536061</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0001222738323938621</v>
+        <v>0.0002198707767517505</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.001789306459427412</v>
+        <v>0.001325616499190581</v>
       </c>
       <c r="CD3" t="n">
-        <v>-4.187118520373456e-05</v>
+        <v>-0.00012777215722375</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0003814115648020244</v>
+        <v>0.0002807100103318594</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.001065002187102688</v>
+        <v>0.0007705873016005416</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.001583764956474446</v>
+        <v>0.002476078299936839</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0004090345051823619</v>
+        <v>-0.0001896665293803346</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0003724277633479467</v>
+        <v>0.001378422985554852</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.001073365421771451</v>
+        <v>0.001279874913219819</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0003116775732023302</v>
+        <v>0.0005026530870167056</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004118786451012066</v>
+        <v>0.004190768261617406</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004440427600700926</v>
+        <v>0.006906371615585511</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004146765279504761</v>
+        <v>0.004358343759737942</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001757928639251656</v>
+        <v>0.0063045968571407</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002628175562057449</v>
+        <v>0.007985325211323996</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002552490028919274</v>
+        <v>0.004578598457280163</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004734674819468454</v>
+        <v>0.0004040851092541599</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006530333579013615</v>
+        <v>0.006325534269825807</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008312292878597981</v>
+        <v>0.01430635464684344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01218541377478244</v>
+        <v>0.01512498654002351</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005499467026218879</v>
+        <v>0.003240260299983701</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00285358089710522</v>
+        <v>0.00660963655712624</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006064667723778228</v>
+        <v>0.005787135749042698</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01376766062553771</v>
+        <v>0.009465187909620174</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01292143464192894</v>
+        <v>0.01185729173479726</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00326821388577883</v>
+        <v>0.003079242706033229</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003836606068298871</v>
+        <v>0.004511600061034439</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005710389897338756</v>
+        <v>0.005510860951770959</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003602465024106212</v>
+        <v>0.005058868155317324</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002713315468020763</v>
+        <v>0.0005263855723947664</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008131359228350874</v>
+        <v>0.005648779642683084</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004828297069368079</v>
+        <v>0.003824088142346554</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002616001425981856</v>
+        <v>0.004125120243514706</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002186087188541012</v>
+        <v>0.003043092433126874</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004147466167418492</v>
+        <v>0.005355916495275681</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0004176666930802474</v>
+        <v>0.0008471722297756447</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.006963460936727821</v>
+        <v>0.009405168781907256</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.01142004082810546</v>
+        <v>0.004689993508461286</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.005249388661622989</v>
+        <v>0.002924657330369755</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005460646486198995</v>
+        <v>0.008402380828453026</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001497599874259705</v>
+        <v>0.0008086903102763891</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0005752581900119233</v>
+        <v>0.0008689158154574813</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004666034492130133</v>
+        <v>0.006605325621410134</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.004641119498668185</v>
+        <v>0.00460906519799883</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001758989170140796</v>
+        <v>0.001585196092288827</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001981924178403737</v>
+        <v>0.0008596055857898704</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.004451067303062235</v>
+        <v>0.003405303832898279</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004239227197494866</v>
+        <v>0.003977986275522451</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001313605185174493</v>
+        <v>0.001199475638401523</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003170896595674653</v>
+        <v>0.002684978676717706</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.00245356749024371</v>
+        <v>0.003989001329417231</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.004110610219023049</v>
+        <v>0.004229833963877497</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.008421338550084973</v>
+        <v>0.007345690489455312</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0112069018769432</v>
+        <v>0.01061724876515292</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.003083881149809671</v>
+        <v>0.003239818799598481</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002866341860288987</v>
+        <v>0.00425106519961936</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0006357271521036484</v>
+        <v>0.0006928531682626987</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003714377523576096</v>
+        <v>0.003296060824305583</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.00463253635679</v>
+        <v>0.005847817867714595</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.005664693768445668</v>
+        <v>0.004294712349200249</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.008472380690899898</v>
+        <v>0.01102938357157622</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0007990004620258409</v>
+        <v>0.0007996948532332693</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0007503400386658796</v>
+        <v>0.0009432910532697074</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002116908368711653</v>
+        <v>0.0007567618888332296</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.004926197770902876</v>
+        <v>0.008856925576249102</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.005689582840215989</v>
+        <v>0.007874277288507934</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001223849759309722</v>
+        <v>0.0009401322679479798</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.00427810137831209</v>
+        <v>0.006998700418924979</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.005877090448774786</v>
+        <v>0.01042547141092001</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001199715898861378</v>
+        <v>0.0008381784433719814</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.005508733717983578</v>
+        <v>0.00442897266298397</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.005144299088600188</v>
+        <v>0.008965371174298182</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.00589889186203156</v>
+        <v>0.008730833715983145</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.005049562208125954</v>
+        <v>0.003929126361258715</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0002407185545671452</v>
+        <v>0.0003850769729474185</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.005118264802564484</v>
+        <v>0.002359118831654228</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0038405969855208</v>
+        <v>0.003900709452666123</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001048870515092002</v>
+        <v>0.001633735317408369</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.01038823171203975</v>
+        <v>0.008942438193496332</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003073507104728306</v>
+        <v>0.001777712428790547</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.006407249606560506</v>
+        <v>0.00502602254037956</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0001636159024802246</v>
+        <v>0.0002343458618370571</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001741103116968536</v>
+        <v>0.000972493039236642</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001151881483600486</v>
+        <v>0.001362787029816853</v>
       </c>
       <c r="CA4" t="n">
         <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001502694887853358</v>
+        <v>0.0005897193586278877</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.00231823188266107</v>
+        <v>0.002770786547143796</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0001218310279658155</v>
+        <v>0.0002828909002876819</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001118116828989749</v>
+        <v>0.0007669975510495058</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001924010677920151</v>
+        <v>0.001525147920001376</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004185734705518415</v>
+        <v>0.003816139102767454</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.00263589315409689</v>
+        <v>0.001493228015295925</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002285625859621851</v>
+        <v>0.003604930708092409</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.004483528237644485</v>
+        <v>0.005426166206493137</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001967618103262861</v>
+        <v>0.001516920459667893</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.003661119515884948</v>
+        <v>-0.005902560899437781</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.006596066565809333</v>
+        <v>-0.008350983358547637</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.00849432689359092</v>
+        <v>-0.006021180030257245</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002947773149631528</v>
+        <v>-0.01597669426556266</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.006578115117014583</v>
+        <v>-0.01767868437697661</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.003509833585476496</v>
+        <v>-0.004739195230998539</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.001165286721864434</v>
+        <v>-0.0001885606536769502</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01565464895635676</v>
+        <v>-0.01100569259962048</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.008147487362473994</v>
+        <v>-0.0228772829221403</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.007882089074014742</v>
+        <v>-0.01505927587311755</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01445639187574676</v>
+        <v>-0.004934415990006191</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.002656546489563582</v>
+        <v>-0.007339163023110495</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.003763440860215095</v>
+        <v>-0.004841149773071152</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01933166770768272</v>
+        <v>-0.006121174266083651</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.012624158923422</v>
+        <v>-0.009277430865298831</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.007843137254901988</v>
+        <v>-0.003614097968936647</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.00211800302571854</v>
+        <v>-0.005446972124319072</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01457938013915245</v>
+        <v>-0.0110702238577123</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.00287792536369389</v>
+        <v>-0.009993674889310567</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0004236006051437258</v>
+        <v>-0.0009113764927718537</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01624810892586983</v>
+        <v>-0.008154121863799269</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.008577599506325251</v>
+        <v>-0.007175712971481107</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.004116907605279718</v>
+        <v>-0.003460429349567406</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.002238577123581698</v>
+        <v>-0.004101249599487333</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.009553739786297954</v>
+        <v>-0.006664609688367851</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001131363922061612</v>
+        <v>-0.0008022215365628526</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.007939339875111528</v>
+        <v>-0.003495860165593334</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01663066954643633</v>
+        <v>-0.01027460660290037</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01430704898446839</v>
+        <v>-0.006807727690892329</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.009441530391854424</v>
+        <v>-0.01340079730144123</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.003573687539531978</v>
+        <v>-0.001471941122355058</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001463560334528136</v>
+        <v>-0.001135005973715619</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.008768070395977379</v>
+        <v>-0.01346212818153937</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01221624850657114</v>
+        <v>-0.00950323974082079</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.003755588673621446</v>
+        <v>-0.003219076005961274</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.0004778972520908309</v>
+        <v>-0.001467832604622121</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.009962287869264608</v>
+        <v>-0.003973085549503319</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.007775377969762465</v>
+        <v>-0.009595803764270328</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.003858317520556609</v>
+        <v>-0.002210274790919931</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.005311125078566947</v>
+        <v>-0.004293495674463288</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.003652675424543406</v>
+        <v>-0.009230297454768421</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.00487023389939123</v>
+        <v>-0.004133214391911976</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.015639374425023</v>
+        <v>-0.01367678626188281</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.0140224859462836</v>
+        <v>-0.0110243597751405</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.005625392834695164</v>
+        <v>-0.00260842237586425</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.003605313092979135</v>
+        <v>-0.006767868437697677</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001570009612303747</v>
+        <v>-0.001319924575738529</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.006913890634820885</v>
+        <v>-0.006255749770009145</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.01149954001839927</v>
+        <v>-0.01162220177859549</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01275388291517328</v>
+        <v>-0.01084756483238457</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.02045384851272615</v>
+        <v>-0.02388837779822135</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0006557377049180247</v>
+        <v>-0.001414204902576988</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0007542426147077342</v>
+        <v>-0.001922460749759636</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.005692599620493366</v>
+        <v>-0.001771030993042366</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.01379944802207911</v>
+        <v>-0.01649800674639677</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01171419809874272</v>
+        <v>-0.01950321987120508</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001141622955877864</v>
+        <v>-0.002210829862223596</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.009614168247944366</v>
+        <v>-0.01559139784946235</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.02066850659306961</v>
+        <v>-0.02187779433681077</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.002324888226527555</v>
+        <v>-0.001319924575738529</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01318785578747629</v>
+        <v>-0.01087919038583176</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01842992946948788</v>
+        <v>-0.02532965348052741</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.01166306695464365</v>
+        <v>-0.01168019987507805</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.006152404747033146</v>
+        <v>-0.003067678684376962</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.000377121307353856</v>
+        <v>-0.0003456945317410587</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.004750378214825957</v>
+        <v>-0.002904689863842691</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.008781362007168492</v>
+        <v>-0.009962523422860669</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.002074167190446286</v>
+        <v>-0.002742175856929985</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.009591527987897109</v>
+        <v>-0.004478063540090815</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.004236006051437147</v>
+        <v>-0.0007168458781361853</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.008199697428139151</v>
+        <v>-0.003691376701966753</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0001581277672359493</v>
+        <v>-0.0004085480829666865</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.00163419233186678</v>
+        <v>-0.002178517397882018</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.002178517397881929</v>
+        <v>-0.0008774583963691463</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.003771213073538671</v>
+        <v>-0.0004538577912254205</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.001785173978819932</v>
+        <v>-0.003257432005060079</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.0003874813710879388</v>
+        <v>-0.0009113764927718759</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.002844175491679202</v>
+        <v>-0.0005446293494705045</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.004148334380892538</v>
+        <v>-0.001281669150521647</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.005688246385920803</v>
+        <v>-0.003904619970193757</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002199874292897586</v>
+        <v>-0.002210274790919931</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.003841349156777041</v>
+        <v>-0.00567502986857823</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.007776096822995427</v>
+        <v>-0.003747657713928765</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.003456945317410454</v>
+        <v>-0.0008028545941123899</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002297926429143077</v>
+        <v>-0.002820683590404605</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.004900104349833509</v>
+        <v>0.0006694263559068131</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.00280044119999662</v>
+        <v>3.809080250985751e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001563491898501418</v>
+        <v>-0.003035647746272488</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0004904392252176204</v>
+        <v>0.001398796507156122</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0008172613307618316</v>
+        <v>-0.001178810734330449</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0003043556872312475</v>
+        <v>-5.158906060056811e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001805326926798981</v>
+        <v>-0.004537525709360155</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.001487932801119113</v>
+        <v>0.002591356319080732</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001171054452752568</v>
+        <v>0.005957351346354581</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.004542950450123323</v>
+        <v>-0.002172605839147473</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0006543630762082836</v>
+        <v>-0.002064885093822452</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.002205462159728413</v>
+        <v>-0.0004897228637192164</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.005781987888438075</v>
+        <v>0.002729100513398855</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001159182215732477</v>
+        <v>3.401737759349543e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.005362172983600516</v>
+        <v>-0.001396732281317178</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0003858120565814971</v>
+        <v>-0.003494081013360595</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.002928591283134929</v>
+        <v>-0.004750368818420786</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.00136429020744884</v>
+        <v>-0.0004336989005505054</v>
       </c>
       <c r="V6" t="n">
-        <v>2.230151650308432e-05</v>
+        <v>7.175688694405217e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.002418712032991335</v>
+        <v>-0.004672476087896291</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.004749518063140612</v>
+        <v>-0.002138350470919803</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0003277478009039131</v>
+        <v>-0.0004713857860487364</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.830681131473666e-05</v>
+        <v>-0.001279119516158941</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.002191502388177047</v>
+        <v>-0.002346173909104687</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0004560980649527368</v>
+        <v>-0.0005536730435841658</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0007810569062007861</v>
+        <v>-0.001250534270203588</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.006123875883019545</v>
+        <v>-0.004992633181975686</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.005305307997491881</v>
+        <v>-0.003830652568899634</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001499796968272743</v>
+        <v>-0.004388805866013387</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.001624726548620664</v>
+        <v>-0.000572997238135961</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0006296464840121862</v>
+        <v>-0.0006983363601921922</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.002642000353825188</v>
+        <v>-0.006318396406935493</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.001443639339196481</v>
+        <v>-0.004432763218760546</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.002077265537076012</v>
+        <v>-0.001040719282044608</v>
       </c>
       <c r="AM6" t="n">
-        <v>-4.654941705078408e-05</v>
+        <v>-0.0005277642608850386</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.002259264810519318</v>
+        <v>-0.0008603983307669343</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.002308226157846657</v>
+        <v>-0.004596247100990903</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.001348972442111196</v>
+        <v>0.000166372604954465</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.001715720169287013</v>
+        <v>-0.001335351912980137</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.002286263967952809</v>
+        <v>-0.003879155647488564</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.002604133407678333</v>
+        <v>-0.0004994434825979554</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.008991097464219854</v>
+        <v>-0.008486622757646695</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.002258399456779936</v>
+        <v>-0.005888474710561614</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0005706140044325931</v>
+        <v>-0.001810435112233408</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0007131139511441953</v>
+        <v>-0.001052549436598049</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.000102517688523554</v>
+        <v>-0.0005197187572472783</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.001435629645440173</v>
+        <v>-0.002427700135733585</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.003796562971540721</v>
+        <v>-0.005889434520022144</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.009213145434578636</v>
+        <v>-0.00689708243429308</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.01297196933464387</v>
+        <v>-0.009779716853831021</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0002087239016521136</v>
+        <v>-0.0006270593955431198</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0005121167341213705</v>
+        <v>-0.0003248557689078752</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.002436025563167887</v>
+        <v>-0.0006956394501200281</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.008320046681350496</v>
+        <v>-0.007889126688968318</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.003218510154995408</v>
+        <v>-0.005127497876704639</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0007239702685234329</v>
+        <v>-0.0002729431964434981</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.001081686234239196</v>
+        <v>-0.00293708363945071</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.007283457848413566</v>
+        <v>-0.01013790123686663</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0006525031496348033</v>
+        <v>-0.0006788980850580022</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.003824382107697816</v>
+        <v>5.727153667287033e-06</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.01034046981861438</v>
+        <v>-0.004198767959911481</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0008006161865682343</v>
+        <v>-0.001626834069350291</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0005900660258140927</v>
+        <v>-0.001316220677520277</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.0001374952071783508</v>
+        <v>-0.0001182995210536247</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001707779886148028</v>
+        <v>0.0009175049406185493</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.002637199140854615</v>
+        <v>-0.0007136592481698207</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0006555122415344006</v>
+        <v>-0.0007564160959553811</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.001698471321608799</v>
+        <v>0.001173610716501064</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.002967483360534101</v>
+        <v>0.0002898637230319745</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.96753671057421e-05</v>
+        <v>-0.001915973757885522</v>
       </c>
       <c r="BX6" t="n">
-        <v>-9.370932516563623e-05</v>
+        <v>-0.0001413138418300541</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001038748953499222</v>
+        <v>-0.0001127761477220962</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0006877727195542555</v>
+        <v>-0.0003956171282375048</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.663666749496806e-05</v>
+        <v>-0.0002539554239423147</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0006003598584682718</v>
+        <v>-4.984102576318095e-05</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0.0001043530670712112</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0003289862290497964</v>
+        <v>-0.000415424935672809</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.002570470069110042</v>
+        <v>-0.0003016384738180472</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.001388313804150387</v>
+        <v>0.0007899927802822809</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.001311174220390696</v>
+        <v>-0.001297586243041854</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0009009677938651094</v>
+        <v>0.0003195012460124713</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.0003722328800223968</v>
+        <v>-0.003191400375622019</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0008078985240881019</v>
+        <v>-0.0005683654617947065</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0002217432425904942</v>
+        <v>-0.001313563094366904</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.003972301772291759</v>
+        <v>0.003287058398988241</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003299133284869637</v>
+        <v>0.001642433856615438</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0004923018302182891</v>
+        <v>-0.0005289032680281968</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001688947994412271</v>
+        <v>0.002897099223572691</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000701011766778442</v>
+        <v>0.001354589080193946</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0001213218675952865</v>
+        <v>0.0003973967133338863</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001787983999549236</v>
+        <v>-0.002121367504962002</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003203398408237934</v>
+        <v>0.007102678268125339</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01102751949445047</v>
+        <v>0.01558037429377022</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.00224971580467877</v>
+        <v>-0.0003769102491606835</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001970799634983977</v>
+        <v>0.001629242245716933</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003010113158545103</v>
+        <v>0.005330605302819796</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.001984735527122849</v>
+        <v>0.003575436678081206</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005596057751235106</v>
+        <v>0.004265654486383125</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.004057857795298325</v>
+        <v>0.0003032504773722522</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001323177159513306</v>
+        <v>-0.001713687902836519</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0001062328536487522</v>
+        <v>-0.001043281281693814</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002957992194051779</v>
+        <v>0.0008383300876360911</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001253458953427156</v>
+        <v>0.0001823981099741079</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0004565951624952824</v>
+        <v>-0.0002547483105544645</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0002275118073517601</v>
+        <v>-0.0006852678498493192</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002060213444503784</v>
+        <v>0.001778218840396351</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001480028172823711</v>
+        <v>0.0001251350013216246</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0008350049289684025</v>
+        <v>-0.0004350676233241813</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.000164849031216735</v>
+        <v>-2.869169384908111e-05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.005305022198459452</v>
+        <v>0.002401744997305144</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.003877364219601625</v>
+        <v>-0.001602874675045468</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0007378094817819093</v>
+        <v>-0.001995380647124312</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0001106894370651479</v>
+        <v>-0.001835121118420363</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.000270976155474556</v>
+        <v>0.0001371297317854014</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0001859128670906318</v>
+        <v>9.179219316352572e-05</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.00184695360092545</v>
+        <v>-0.0002666730989826227</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.0002524966131599637</v>
+        <v>-0.001707815050162836</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0005099031733895975</v>
+        <v>-0.0004030763677391524</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0001983540705196851</v>
+        <v>-0.0003692153044105584</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.000645978584966267</v>
+        <v>0.00251922669265015</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0007988754833087807</v>
+        <v>-0.0006850733534954856</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0003665425805273848</v>
+        <v>0.0003672686517907364</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.460303300622969e-05</v>
+        <v>0.0009432064941012841</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.25747642370085e-06</v>
+        <v>-0.001258088472316393</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.000227317503438712</v>
+        <v>0.001268199356512417</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.006762134607875859</v>
+        <v>-0.005345711064559056</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.0009878859766522252</v>
+        <v>0.001635098752837288</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.001463091639878855</v>
+        <v>0.0004262893029504001</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.001931661135311902</v>
+        <v>0.0003186262985456712</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.000121931672573794</v>
+        <v>-0.0001785893919673765</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.55859004218418e-05</v>
+        <v>0.0004067572083665483</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.001072088371854518</v>
+        <v>-0.003413822472130118</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.003532977750393435</v>
+        <v>-0.004533120873720636</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.005722837777157641</v>
+        <v>-0.0007656652440418965</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0001065125322369909</v>
+        <v>1.41201148628034e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0001186774512293043</v>
+        <v>-1.903338909375863e-06</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.0001412241955942806</v>
+        <v>-0.0001336117403571257</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.006407050762711553</v>
+        <v>-0.003775696902154901</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0009000555944286171</v>
+        <v>-0.003616104081556215</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.0003685597024423115</v>
+        <v>-0.0001849496485271607</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.0001375960493240958</v>
+        <v>0.001399076309536151</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.006137992831541251</v>
+        <v>-0.001087350921596764</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0002605616231999786</v>
+        <v>-0.0003606822443445956</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.00159338953769802</v>
+        <v>0.001207279406827649</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.006599698772469897</v>
+        <v>-0.002544377612958726</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.002096413081073683</v>
+        <v>0.004842205415025341</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.002887385956110938</v>
+        <v>0.001233171536368427</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-6.217844144862928e-05</v>
+        <v>2.858252675826955e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.001118233275821839</v>
+        <v>0.002207646617135817</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.0002149139260049227</v>
+        <v>0.0007531652167642178</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.722864102300832e-05</v>
+        <v>-0.0002958420076688284</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.005045519131503734</v>
+        <v>0.005629066394478144</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.0006073871637185036</v>
+        <v>0.001534245367515053</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.002711978978489271</v>
+        <v>-0.0005599996565197718</v>
       </c>
       <c r="BX7" t="n">
-        <v>-4.548381873039076e-05</v>
+        <v>7.829300465396206e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0004564962093458136</v>
+        <v>4.68751807311929e-05</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-5.783441977409985e-05</v>
+        <v>0.0001311499507901049</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0003728909479822906</v>
+        <v>0.0001234586219896805</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.001342096174987506</v>
+        <v>0.001008492660501809</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>3.08546744831717e-05</v>
+        <v>0.0002583471160971684</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0005766790007566691</v>
+        <v>0.000117375929117397</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.001993971141023782</v>
+        <v>0.002365249801297903</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0003613024065660275</v>
+        <v>-0.0001212470785084519</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.001488434010333362</v>
+        <v>0.001642758587097121</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001240403897345421</v>
+        <v>-0.0004805600913813879</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.000304069468249113</v>
+        <v>-0.0002409407805288421</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.004337678744077453</v>
+        <v>0.001626158085558946</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0007366544469948749</v>
+        <v>0.005847067477485864</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002014033510010968</v>
+        <v>0.003602771088486997</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0004082523357725298</v>
+        <v>0.002667144113546566</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009553121937654591</v>
+        <v>0.007476408512573546</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001886345226788738</v>
+        <v>0.003450392118920872</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001960935053582663</v>
+        <v>0.0005523218544065456</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003813703824300641</v>
+        <v>0.001208578330279908</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01096079787670825</v>
+        <v>0.01781460445598546</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01531918734188048</v>
+        <v>0.02413029728020244</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001637952178912419</v>
+        <v>0.0004054278713183868</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001188220893007699</v>
+        <v>0.003429401332540142</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007322295770806428</v>
+        <v>0.007894222282815369</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01380940698818338</v>
+        <v>0.01153003644726962</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01349676347799778</v>
+        <v>0.01172417011248041</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.000442915450152756</v>
+        <v>0.002857292632316993</v>
       </c>
       <c r="S8" t="n">
-        <v>0.005480444866118464</v>
+        <v>0.002337527843212691</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002647846646346228</v>
+        <v>0.001527723312112999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.005052151819645226</v>
+        <v>0.00299880264085613</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0003650327125866326</v>
+        <v>0.0004761465462130965</v>
       </c>
       <c r="W8" t="n">
-        <v>0.006581278845218533</v>
+        <v>0.003548883029063621</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00332338358822096</v>
+        <v>-0.0002852005585238015</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003147069436087621</v>
+        <v>0.00448317510199942</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00264288778285644</v>
+        <v>0.002028181190977216</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001954959082683824</v>
+        <v>0.001707514346327088</v>
       </c>
       <c r="AB8" t="n">
-        <v>-6.047672868201847e-05</v>
+        <v>0.0006022707575383424</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.007251559101315752</v>
+        <v>0.00594915993994202</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.001586159316182761</v>
+        <v>0.0008698214902942147</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.001742953087539853</v>
+        <v>-0.0004738451201832638</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.00473628105311458</v>
+        <v>0.00290353909446894</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0002480379717966996</v>
+        <v>0.0006919465147285976</v>
       </c>
       <c r="AH8" t="n">
-        <v>-5.382726779133429e-05</v>
+        <v>0.0007305598806842228</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001382102695671791</v>
+        <v>0.002377934963907325</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.001274310603327322</v>
+        <v>0.001779499772403781</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0003234348694981931</v>
+        <v>0.000181520279051603</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.001319242623401759</v>
+        <v>6.638768215052881e-05</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002838922194840948</v>
+        <v>0.003858105931215994</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0008625862201594919</v>
+        <v>0.001030916052748654</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.000199360407337737</v>
+        <v>0.001022815819660439</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002224591389365687</v>
+        <v>0.00240023597160304</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.001859540994242151</v>
+        <v>0.0007290694095611228</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001023242225559262</v>
+        <v>0.004185263945717419</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0007789194889046863</v>
+        <v>0.002196633432930278</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.003210030088240412</v>
+        <v>0.01007435627910054</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.003389388385507908</v>
+        <v>0.001282445932463078</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.002848578353104445</v>
+        <v>0.002645304215486588</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0004067276065647191</v>
+        <v>0.0005171266316450485</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.002395854315942911</v>
+        <v>0.001065372832949543</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001232233472327188</v>
+        <v>0.001810129976579686</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.91059869566741e-06</v>
+        <v>-0.002645838715916435</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.297999791395672e-05</v>
+        <v>0.004155508460814689</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0002025283680883588</v>
+        <v>0.0003834604706167949</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0003716961342033615</v>
+        <v>0.0004984608242316723</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.687242602474665e-05</v>
+        <v>0.000297424457351933</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.0006324949655198669</v>
+        <v>0.004516667768809155</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.0004942505099398336</v>
+        <v>-0.0005062611075347251</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0008396917961064786</v>
+        <v>0.0003314412266373218</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002220929227563298</v>
+        <v>0.003299199715675027</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0.00235008118323998</v>
+        <v>0.0003377685010186981</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0009744990018938803</v>
+        <v>-1.493428912783812e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>3.42699742491237e-05</v>
+        <v>0.003311568036099014</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0.00423736207003588</v>
+        <v>0.0004597818097448525</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.004022911398218823</v>
+        <v>0.01100619159695035</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.004122821245851982</v>
+        <v>0.005505886718002654</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0002235936840643327</v>
+        <v>0.0004000623531126458</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.004338953144141722</v>
+        <v>0.003368521453029241</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001149525155296491</v>
+        <v>0.001926281472592134</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.000689102164622693</v>
+        <v>2.398049522163159e-05</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.01452477378731208</v>
+        <v>0.01479327651947921</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001799334593841542</v>
+        <v>0.002783438697765514</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.004152351737771109</v>
+        <v>0.003135668440944309</v>
       </c>
       <c r="BX8" t="n">
-        <v>2.235469448584326e-05</v>
+        <v>0.0002338648111955194</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.001472970518222064</v>
+        <v>0.0008258211733517013</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0008061711776677111</v>
+        <v>0.001054003133287595</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0006821415223892014</v>
+        <v>0.0005292310756544405</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.002642750731562627</v>
+        <v>0.002640471577156855</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0002892285226944708</v>
+        <v>0.0006252047980674164</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0005682998486511881</v>
+        <v>0.002042483660130745</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.004361839331043968</v>
+        <v>0.003890969055191426</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0008599177810924396</v>
+        <v>0.0001507222719494189</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001705066735896302</v>
+        <v>0.003438249202590315</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.003918933164663674</v>
+        <v>0.00439513582109112</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0008922217431353296</v>
+        <v>0.001480817199833256</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007151780137414054</v>
+        <v>0.009009564949089754</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00719832735961764</v>
+        <v>0.01563601409804553</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006589631480324732</v>
+        <v>0.01111823133611027</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002468034493012172</v>
+        <v>0.005585424133811257</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002998126171142956</v>
+        <v>0.01089943785134294</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005430422709040372</v>
+        <v>0.01110768281394627</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005376344086021279</v>
+        <v>0.0009256402344954839</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00708371665133396</v>
+        <v>0.01082999074359763</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01640477686989313</v>
+        <v>0.02858019012572836</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03097209444955538</v>
+        <v>0.03342532965348057</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00470938897168407</v>
+        <v>0.005553841406973126</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006777014366021172</v>
+        <v>0.01614867029798146</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01292810860845415</v>
+        <v>0.01076578019865431</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02342771982116246</v>
+        <v>0.02554396423248879</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02991829038340664</v>
+        <v>0.02870370370370375</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001505927587311773</v>
+        <v>0.005458448328733568</v>
       </c>
       <c r="S9" t="n">
-        <v>0.008678319533885315</v>
+        <v>0.009050911376492776</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005543964232488841</v>
+        <v>0.004172876304023821</v>
       </c>
       <c r="U9" t="n">
-        <v>0.00609679446888749</v>
+        <v>0.007867941993211947</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0004684572142411025</v>
+        <v>0.0009873495834618496</v>
       </c>
       <c r="W9" t="n">
-        <v>0.008279668813247498</v>
+        <v>0.009132983647022475</v>
       </c>
       <c r="X9" t="n">
-        <v>0.005277951280449644</v>
+        <v>0.007511177347242904</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004928315412186324</v>
+        <v>0.01015084852294154</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004411326378539493</v>
+        <v>0.00539493293591653</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003733415612465263</v>
+        <v>0.009955290611028279</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0003874813710879388</v>
+        <v>0.001948460087994985</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0151155527795128</v>
+        <v>0.02835544585004623</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0243285446595877</v>
+        <v>0.00424734540911933</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.002325581395348819</v>
+        <v>0.002595322012175627</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.006766020864381527</v>
+        <v>0.01603942652329753</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0003066544004906691</v>
+        <v>0.0008651073373919238</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0006788028386300104</v>
+        <v>0.001377763537327825</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.006690454950936664</v>
+        <v>0.009438470728793325</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.003040238450074539</v>
+        <v>0.004682589566310491</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.00203640851589012</v>
+        <v>0.002499228633137873</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.00601666152422089</v>
+        <v>0.001341281669150496</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.005550444648880726</v>
+        <v>0.005704898446833961</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.005752608047690034</v>
+        <v>0.001427297056199828</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0006746396810794475</v>
+        <v>0.001877794336810701</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.005506807866868435</v>
+        <v>0.003434886499402667</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.003310430980637025</v>
+        <v>0.003368107302533507</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.009842641160135723</v>
+        <v>0.01092255476704717</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.01314217443249696</v>
+        <v>0.006933166770768317</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.02795698924731178</v>
+        <v>0.02123655913978496</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.004838709677419317</v>
+        <v>0.008286140089418758</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.006945317410433682</v>
+        <v>0.007332339791356146</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0006354009077155886</v>
+        <v>0.0008855154965212054</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.006071757129714838</v>
+        <v>0.004977645305514133</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.004360812425328519</v>
+        <v>0.007432854465958827</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.002873204247345351</v>
+        <v>0.002092442223610258</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.00324888226527571</v>
+        <v>0.0144862604540024</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001854179761156494</v>
+        <v>0.001234186979327312</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001728763040238457</v>
+        <v>0.001106894370651468</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0003524511374559447</v>
+        <v>0.0007228158390948924</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0007906388361796246</v>
+        <v>0.01290322580645164</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.006690561529271166</v>
+        <v>0.008525921299188065</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.002734129478315506</v>
+        <v>0.001099937146448759</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.006942301758716396</v>
+        <v>0.006356062943535923</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0005446293494705045</v>
+        <v>0.01177389131792633</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001436602123672692</v>
+        <v>0.001295896328293678</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.006945317410433705</v>
+        <v>0.004431175361407913</v>
       </c>
       <c r="BN9" t="n">
-        <v>-0.001549652118912093</v>
+        <v>0.00809438470728795</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.008852459016393454</v>
+        <v>0.0141278375149343</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01303281202085251</v>
+        <v>0.0074210364918737</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0003394014193150108</v>
+        <v>0.0007666360012266616</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01281815394050905</v>
+        <v>0.005263157894736858</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.003587856485740581</v>
+        <v>0.003597977995837065</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001110768281394581</v>
+        <v>0.002702702702702708</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.02640382317801667</v>
+        <v>0.02329749103942657</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.004446488807114424</v>
+        <v>0.004477154247163495</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01247642991829037</v>
+        <v>0.01059082338152104</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0003933434190620311</v>
+        <v>0.00032041012495998</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.003587856485740581</v>
+        <v>0.001124297314178646</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.001780137414116156</v>
+        <v>0.003802514566084081</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001870591842992975</v>
+        <v>0.001217988757026867</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.005584696081456319</v>
+        <v>0.005394932935916519</v>
       </c>
       <c r="CD9" t="n">
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0004906470407850638</v>
+        <v>0.001834282099936757</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.001192250372578274</v>
+        <v>0.003236957888120673</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.008279668813247487</v>
+        <v>0.008393070489844723</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.00622508432996014</v>
+        <v>0.002308665401644538</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002859836580766806</v>
+        <v>0.007329040171726508</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.006599622878692635</v>
+        <v>0.01081081081081081</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.003010432190760093</v>
+        <v>0.003695976154992531</v>
       </c>
     </row>
   </sheetData>
